--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N88_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N88_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.94315838868183</v>
+        <v>7.303263238160798</v>
       </c>
       <c r="D2" t="n">
-        <v>45.57979021664137</v>
+        <v>7.406715910204223</v>
       </c>
       <c r="E2" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F2" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.40856641444616</v>
+        <v>5.916392042347501</v>
       </c>
       <c r="D3" t="n">
-        <v>35.74775538689462</v>
+        <v>5.809010250370377</v>
       </c>
       <c r="E3" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F3" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>4.136688760006813</v>
+        <v>0.6722119235011073</v>
       </c>
       <c r="D4" t="n">
-        <v>7.215182551201705</v>
+        <v>1.172467164570277</v>
       </c>
       <c r="E4" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F4" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.12235969856828</v>
+        <v>1.969883451017346</v>
       </c>
       <c r="D5" t="n">
-        <v>3.666771884012247</v>
+        <v>0.5958504311519902</v>
       </c>
       <c r="E5" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F5" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.2002747232013</v>
+        <v>2.957544642520211</v>
       </c>
       <c r="D6" t="n">
-        <v>18.2002747232013</v>
+        <v>2.957544642520211</v>
       </c>
       <c r="E6" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F6" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.43260937590602</v>
+        <v>5.757799023584728</v>
       </c>
       <c r="D7" t="n">
-        <v>35.67020514286155</v>
+        <v>5.796408335715002</v>
       </c>
       <c r="E7" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F7" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>43.72928080817245</v>
+        <v>7.106008131328024</v>
       </c>
       <c r="D8" t="n">
-        <v>43.72928080817245</v>
+        <v>7.106008131328024</v>
       </c>
       <c r="E8" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F8" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.94059721326836</v>
+        <v>8.27784704715611</v>
       </c>
       <c r="D9" t="n">
-        <v>50.94059721326836</v>
+        <v>8.27784704715611</v>
       </c>
       <c r="E9" t="n">
-        <v>15.98540695434898</v>
+        <v>2.59762863008171</v>
       </c>
       <c r="F9" t="n">
-        <v>16.90661699095282</v>
+        <v>2.747325261029833</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
